--- a/storage/files/users.sample.xlsx
+++ b/storage/files/users.sample.xlsx
@@ -16,147 +16,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
-    <t>Id</t>
+    <t>編號</t>
   </si>
   <si>
-    <t>Name</t>
+    <t>姓名</t>
   </si>
   <si>
-    <t>Email</t>
+    <t>電子郵件</t>
   </si>
   <si>
-    <t>Email Verified At</t>
+    <t>電子郵件驗證時間</t>
   </si>
   <si>
-    <t>Created At</t>
+    <t>建立時間</t>
   </si>
   <si>
-    <t>Updated At</t>
-  </si>
-  <si>
-    <t>Terry Lynch DDS</t>
-  </si>
-  <si>
-    <t>gaston.heller@example.com</t>
-  </si>
-  <si>
-    <t>2024-08-29T11:26:05.000000Z</t>
-  </si>
-  <si>
-    <t>2024-08-29T11:26:06.000000Z</t>
-  </si>
-  <si>
-    <t>Prof. Jannie Hirthe</t>
-  </si>
-  <si>
-    <t>lebsack.travis@example.org</t>
-  </si>
-  <si>
-    <t>Jermaine Zemlak</t>
-  </si>
-  <si>
-    <t>lilyan.hilpert@example.com</t>
-  </si>
-  <si>
-    <t>Chloe Kuhn</t>
-  </si>
-  <si>
-    <t>rosalia.hickle@example.net</t>
-  </si>
-  <si>
-    <t>Chanelle Donnelly</t>
-  </si>
-  <si>
-    <t>juvenal.ziemann@example.net</t>
-  </si>
-  <si>
-    <t>Ellie Hills IV</t>
-  </si>
-  <si>
-    <t>lavada.johnston@example.com</t>
-  </si>
-  <si>
-    <t>Abby Watsica DVM</t>
-  </si>
-  <si>
-    <t>eraynor@example.net</t>
-  </si>
-  <si>
-    <t>Darron Simonis</t>
-  </si>
-  <si>
-    <t>karina95@example.com</t>
-  </si>
-  <si>
-    <t>Dr. Leo Padberg MD</t>
-  </si>
-  <si>
-    <t>mhickle@example.net</t>
-  </si>
-  <si>
-    <t>Cecelia D'Amore Jr.</t>
-  </si>
-  <si>
-    <t>ldicki@example.net</t>
-  </si>
-  <si>
-    <t>Monte Maggio</t>
-  </si>
-  <si>
-    <t>hermann.paula@example.com</t>
-  </si>
-  <si>
-    <t>Chelsey Hyatt</t>
-  </si>
-  <si>
-    <t>jonatan.kuhic@example.org</t>
-  </si>
-  <si>
-    <t>Declan Walker</t>
-  </si>
-  <si>
-    <t>cdaniel@example.net</t>
-  </si>
-  <si>
-    <t>2024-08-29T11:26:07.000000Z</t>
-  </si>
-  <si>
-    <t>Doyle D'Amore</t>
-  </si>
-  <si>
-    <t>wpowlowski@example.org</t>
-  </si>
-  <si>
-    <t>Mrs. Princess Sauer DVM</t>
-  </si>
-  <si>
-    <t>santiago63@example.com</t>
-  </si>
-  <si>
-    <t>Mr. Jillian Greenfelder</t>
-  </si>
-  <si>
-    <t>toy.hettinger@example.com</t>
-  </si>
-  <si>
-    <t>Valentine Corkery I</t>
-  </si>
-  <si>
-    <t>adan.streich@example.com</t>
-  </si>
-  <si>
-    <t>Mr. Hyman Bins IV</t>
-  </si>
-  <si>
-    <t>jarvis.upton@example.org</t>
-  </si>
-  <si>
-    <t>Alyson Robel PhD</t>
-  </si>
-  <si>
-    <t>nprosacco@example.com</t>
+    <t>更新時間</t>
   </si>
 </sst>
 </file>
@@ -173,7 +50,6 @@
     <font>
       <color theme="1"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -190,9 +66,12 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -404,6 +283,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="4" max="4" width="23.11"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
@@ -426,384 +308,156 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
     </row>
     <row r="3">
-      <c r="A3" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
     </row>
     <row r="4">
-      <c r="A4" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
     </row>
     <row r="5">
-      <c r="A5" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
     </row>
     <row r="6">
-      <c r="A6" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
     </row>
     <row r="7">
-      <c r="A7" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
     </row>
     <row r="8">
-      <c r="A8" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
     </row>
     <row r="9">
-      <c r="A9" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
     </row>
     <row r="10">
-      <c r="A10" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
     </row>
     <row r="11">
-      <c r="A11" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
     </row>
     <row r="12">
-      <c r="A12" s="1">
-        <v>11.0</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
     </row>
     <row r="13">
-      <c r="A13" s="1">
-        <v>12.0</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
     </row>
     <row r="14">
-      <c r="A14" s="1">
-        <v>13.0</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>34</v>
-      </c>
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
     </row>
     <row r="15">
-      <c r="A15" s="1">
-        <v>14.0</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>34</v>
-      </c>
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
     </row>
     <row r="16">
-      <c r="A16" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>34</v>
-      </c>
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
     </row>
     <row r="17">
-      <c r="A17" s="1">
-        <v>16.0</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>34</v>
-      </c>
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
     </row>
     <row r="18">
-      <c r="A18" s="1">
-        <v>17.0</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>34</v>
-      </c>
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
     </row>
     <row r="19">
-      <c r="A19" s="1">
-        <v>18.0</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>34</v>
-      </c>
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
     </row>
     <row r="20">
-      <c r="A20" s="1">
-        <v>19.0</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>34</v>
-      </c>
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
